--- a/jira_export_2026-09-17.xlsx
+++ b/jira_export_2026-09-17.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>265 h</t>
+          <t>268 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P152"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -948,7 +948,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -2233,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="11" t="inlineStr"/>
@@ -4377,7 +4377,7 @@
         <v>3</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>65.73</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>29.21</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="52">
@@ -7418,32 +7418,32 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7453,34 +7453,34 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7490,12 +7490,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
@@ -7541,16 +7541,16 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O95" s="16" t="n">
         <v>0</v>
@@ -7562,12 +7562,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
@@ -7602,27 +7602,27 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K96" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O96" s="16" t="n">
         <v>0</v>
@@ -7634,32 +7634,32 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7669,32 +7669,32 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7706,27 +7706,27 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
@@ -7746,29 +7746,29 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.75</v>
+        <v>5.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7829,18 +7829,18 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7901,16 +7901,16 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O100" s="16" t="n">
         <v>0</v>
@@ -7922,32 +7922,32 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -7957,35 +7957,35 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="12" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O101" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
         <v>0</v>
@@ -7994,30 +7994,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8027,35 +8029,35 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O102" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P102" s="15" t="n">
         <v>0</v>
@@ -8064,12 +8066,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8079,13 +8081,11 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v/>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
@@ -8104,23 +8104,23 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8403,18 +8403,18 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8424,12 +8424,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8439,11 +8439,13 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E108" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -8457,34 +8459,34 @@
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.5</v>
+        <v>1.55</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8494,12 +8496,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Adaptation Modèle et FDS</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8509,34 +8511,48 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F109" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H109" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr"/>
-      <c r="M109" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8550,12 +8566,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8565,48 +8581,34 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E110" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F110" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F110" s="14" t="inlineStr"/>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H110" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H110" s="14" t="inlineStr"/>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M110" s="14" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
       <c r="N110" s="15" t="n">
         <v>0</v>
       </c>
@@ -8620,12 +8622,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8635,7 +8637,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8653,34 +8655,34 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8690,22 +8692,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8723,34 +8725,34 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8760,22 +8762,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8793,49 +8795,49 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="12" t="n">
-        <v>416.188</v>
+        <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8845,13 +8847,11 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v/>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -8860,54 +8860,54 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P114" s="15" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8917,11 +8917,13 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
@@ -8930,33 +8932,33 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -8972,12 +8974,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8987,7 +8989,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -9010,23 +9012,23 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>14</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9091,12 +9093,12 @@
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
@@ -9127,7 +9129,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9161,12 +9163,12 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
@@ -9197,7 +9199,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9231,12 +9233,12 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9252,12 +9254,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22494</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9267,7 +9269,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9280,27 +9282,35 @@
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L120" s="14" t="inlineStr"/>
-      <c r="M120" s="14" t="inlineStr"/>
+        <v>0.06</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M120" s="14" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N120" s="15" t="n">
         <v>0</v>
       </c>
@@ -9314,12 +9324,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-22494</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9329,7 +9339,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9342,7 +9352,7 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -9352,7 +9362,7 @@
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
@@ -9361,16 +9371,8 @@
       <c r="K121" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L121" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27368</t>
-        </is>
-      </c>
-      <c r="M121" s="11" t="inlineStr">
-        <is>
-          <t>484163</t>
-        </is>
-      </c>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
       <c r="N121" s="12" t="n">
         <v>0</v>
       </c>
@@ -9384,22 +9386,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9422,29 +9424,29 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="15" t="n">
@@ -9454,12 +9456,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21548</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[Evreux] AME</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9469,7 +9471,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9492,29 +9494,29 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28039</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>477841</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O123" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9524,12 +9526,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21548</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Evreux] AME</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9539,7 +9541,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9557,28 +9559,28 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>8.25</v>
+        <v>0.25</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28039</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>477841</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
@@ -9594,22 +9596,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9627,28 +9629,28 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>1</v>
+        <v>8.25</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
@@ -9664,22 +9666,22 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9702,29 +9704,29 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O126" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="15" t="n">
@@ -9734,12 +9736,12 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9749,7 +9751,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9767,34 +9769,34 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O127" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9804,12 +9806,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9819,7 +9821,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9837,12 +9839,12 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
@@ -9853,12 +9855,12 @@
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
@@ -9874,22 +9876,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9907,28 +9909,28 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
@@ -9993,12 +9995,12 @@
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10014,12 +10016,12 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -10029,7 +10031,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10042,27 +10044,35 @@
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L131" s="11" t="inlineStr"/>
-      <c r="M131" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L131" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N131" s="12" t="n">
         <v>0</v>
       </c>
@@ -10076,22 +10086,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10109,7 +10119,7 @@
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
@@ -10121,7 +10131,7 @@
         <v>21</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>12.08</v>
+        <v>6</v>
       </c>
       <c r="L132" s="14" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -10138,22 +10148,22 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10161,44 +10171,36 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M133" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>13.08</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O133" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="12" t="n">
@@ -10208,22 +10210,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10231,7 +10233,7 @@
       </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
@@ -10241,34 +10243,34 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="15" t="n">
@@ -10293,7 +10295,7 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10327,7 +10329,7 @@
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
@@ -10348,12 +10350,12 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
@@ -10363,7 +10365,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10393,22 +10395,22 @@
         <v>21</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="15" t="n">
@@ -10418,22 +10420,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-17710</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Saint Lo] Migration</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Saint Lo</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10441,32 +10443,44 @@
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G137" s="11" t="inlineStr"/>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>25/11/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr"/>
-      <c r="M137" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N137" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O137" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="12" t="n">
@@ -10476,22 +10490,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-16116</t>
+          <t>PDMDEP-17710</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
+          <t>[Saint Lo] Migration</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>Saint Lo</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10499,29 +10513,25 @@
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G138" s="14" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr"/>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>25/11/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10538,22 +10548,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10576,14 +10586,14 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L139" s="11" t="inlineStr"/>
       <c r="M139" s="11" t="inlineStr"/>
@@ -10600,22 +10610,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10638,14 +10648,14 @@
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -10662,22 +10672,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10695,19 +10705,19 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>3.58</v>
+        <v>0.75</v>
       </c>
       <c r="L141" s="11" t="inlineStr"/>
       <c r="M141" s="11" t="inlineStr"/>
@@ -10724,22 +10734,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10752,35 +10762,27 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10794,22 +10796,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10822,23 +10824,35 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H143" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
@@ -10852,12 +10866,12 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
@@ -10867,7 +10881,7 @@
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10883,32 +10897,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H144" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H144" s="14" t="inlineStr"/>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M144" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -10922,28 +10924,26 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v/>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
@@ -10957,12 +10957,12 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
@@ -10971,8 +10971,16 @@
       <c r="K145" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L145" s="11" t="inlineStr"/>
-      <c r="M145" s="11" t="inlineStr"/>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N145" s="12" t="n">
         <v>0</v>
       </c>
@@ -10986,23 +10994,27 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C146" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F146" s="14" t="inlineStr">
@@ -11017,19 +11029,19 @@
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L146" s="14" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -11046,21 +11058,25 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr"/>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11068,26 +11084,26 @@
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H147" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L147" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr"/>
       <c r="M147" s="11" t="inlineStr"/>
       <c r="N147" s="12" t="n">
         <v>0</v>
@@ -11102,18 +11118,18 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr"/>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr"/>
@@ -11124,7 +11140,7 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr"/>
@@ -11137,9 +11153,13 @@
         <v>2</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L148" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M148" s="14" t="inlineStr"/>
       <c r="N148" s="15" t="n">
         <v>0</v>
@@ -11154,18 +11174,18 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr"/>
@@ -11176,31 +11196,23 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L149" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M149" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr"/>
+      <c r="M149" s="11" t="inlineStr"/>
       <c r="N149" s="12" t="n">
         <v>0</v>
       </c>
@@ -11214,18 +11226,18 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr"/>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr"/>
@@ -11242,23 +11254,23 @@
       <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M150" s="14" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N150" s="15" t="n">
@@ -11274,18 +11286,18 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr"/>
@@ -11296,59 +11308,119 @@
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr"/>
       <c r="I151" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J151" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K151" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M151" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N151" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr"/>
+      <c r="D152" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr"/>
+      <c r="F152" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G152" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H152" s="14" t="inlineStr"/>
+      <c r="I152" s="14" t="inlineStr">
+        <is>
           <t>04/04/2025</t>
         </is>
       </c>
-      <c r="J151" s="11" t="n">
+      <c r="J152" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="K151" s="11" t="n">
+      <c r="K152" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L151" s="11" t="inlineStr"/>
-      <c r="M151" s="11" t="inlineStr"/>
-      <c r="N151" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O151" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="17" t="inlineStr">
+      <c r="L152" s="14" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+      <c r="N152" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B152" s="17" t="inlineStr"/>
-      <c r="C152" s="17" t="inlineStr"/>
-      <c r="D152" s="17" t="inlineStr"/>
-      <c r="E152" s="17" t="inlineStr"/>
-      <c r="F152" s="17" t="inlineStr"/>
-      <c r="G152" s="17" t="inlineStr"/>
-      <c r="H152" s="17" t="inlineStr"/>
-      <c r="I152" s="17" t="inlineStr"/>
-      <c r="J152" s="17" t="inlineStr"/>
-      <c r="K152" s="17" t="inlineStr"/>
-      <c r="L152" s="17" t="inlineStr"/>
-      <c r="M152" s="17" t="inlineStr"/>
-      <c r="N152" s="18" t="n">
+      <c r="B153" s="17" t="inlineStr"/>
+      <c r="C153" s="17" t="inlineStr"/>
+      <c r="D153" s="17" t="inlineStr"/>
+      <c r="E153" s="17" t="inlineStr"/>
+      <c r="F153" s="17" t="inlineStr"/>
+      <c r="G153" s="17" t="inlineStr"/>
+      <c r="H153" s="17" t="inlineStr"/>
+      <c r="I153" s="17" t="inlineStr"/>
+      <c r="J153" s="17" t="inlineStr"/>
+      <c r="K153" s="17" t="inlineStr"/>
+      <c r="L153" s="17" t="inlineStr"/>
+      <c r="M153" s="17" t="inlineStr"/>
+      <c r="N153" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O152" s="18" t="n">
+      <c r="O153" s="18" t="n">
         <v>25176.268</v>
       </c>
-      <c r="P152" s="18" t="n">
-        <v>150.92</v>
+      <c r="P153" s="18" t="n">
+        <v>148.91</v>
       </c>
     </row>
   </sheetData>
@@ -11501,6 +11573,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12582,16 +12655,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>85.17</v>
+        <v>85.92</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>27.92</v>
+        <v>28.92</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>123.83</v>
+        <v>126.08</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>20.42</v>
@@ -12601,7 +12674,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.3%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-09-17.xlsx
+++ b/jira_export_2026-09-17.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>268 h</t>
+          <t>272 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4521,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>465.85</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>93.17</v>
+        <v>66.55</v>
       </c>
     </row>
     <row r="54">
@@ -5914,12 +5914,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5954,29 +5954,29 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5986,32 +5986,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K74" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6058,32 +6058,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6093,34 +6093,34 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O75" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6130,32 +6130,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6165,28 +6165,28 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
@@ -6202,12 +6202,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6242,29 +6242,29 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O77" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6274,32 +6274,32 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6309,69 +6309,69 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6381,49 +6381,49 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O79" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P79" s="12" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
@@ -6469,19 +6469,19 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
-        <v>823.65</v>
+        <v>590.15</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
         <v>0</v>
@@ -6490,12 +6490,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
@@ -6541,19 +6541,19 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O81" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <v>823.65</v>
       </c>
       <c r="P81" s="12" t="n">
         <v>0</v>
@@ -6562,32 +6562,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6602,27 +6602,27 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O82" s="16" t="n">
         <v>0</v>
@@ -6634,12 +6634,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6674,27 +6674,27 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6706,32 +6706,32 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
@@ -6757,16 +6757,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6778,12 +6778,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6818,64 +6818,64 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
-        <v>1470</v>
+        <v>588</v>
+      </c>
+      <c r="O85" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
-        <v>452.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31735</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[EVREUX] - Initiation à la redevance</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE EVREUX</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Initiation à la redevance</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6885,69 +6885,69 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.25</v>
+        <v>3.25</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31739</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00158914</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0</v>
+        <v>1470</v>
       </c>
       <c r="P86" s="15" t="n">
-        <v>0</v>
+        <v>452.31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31735</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[EVREUX] - Initiation à la redevance</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE EVREUX</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Initiation à la redevance</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6957,34 +6957,34 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31739</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00158914</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6994,12 +6994,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
@@ -7045,16 +7045,16 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O88" s="16" t="n">
         <v>0</v>
@@ -7066,32 +7066,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7117,16 +7117,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O89" s="16" t="n">
         <v>0</v>
@@ -7138,27 +7138,27 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
@@ -7185,14 +7185,22 @@
         <v>7</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr"/>
-      <c r="M90" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M90" s="14" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7202,12 +7210,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7217,12 +7225,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7232,7 +7240,7 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -7242,25 +7250,17 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L91" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M91" s="11" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr"/>
       <c r="N91" s="12" t="n">
         <v>0</v>
       </c>
@@ -7274,32 +7274,32 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7309,34 +7309,34 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>210</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7346,12 +7346,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7397,19 +7397,19 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
+      </c>
+      <c r="O93" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
         <v>0</v>
@@ -7418,32 +7418,32 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7453,35 +7453,35 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="P94" s="15" t="n">
         <v>0</v>
@@ -7490,32 +7490,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7525,34 +7525,34 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="O95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7562,12 +7562,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
@@ -7613,16 +7613,16 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O96" s="16" t="n">
         <v>0</v>
@@ -7634,12 +7634,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -7674,27 +7674,27 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K97" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7706,32 +7706,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7741,32 +7741,32 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O98" s="16" t="n">
         <v>0</v>
@@ -7778,27 +7778,27 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -7818,29 +7818,29 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.75</v>
+        <v>5.5</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>690</v>
+      </c>
+      <c r="O99" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7850,12 +7850,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -7890,29 +7890,29 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O100" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="15" t="n">
@@ -7973,18 +7973,18 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7994,32 +7994,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8029,35 +8029,35 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="15" t="n">
-        <v>362.5</v>
+        <v>187.5</v>
+      </c>
+      <c r="O102" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
         <v>0</v>
@@ -8066,26 +8066,28 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
@@ -8099,34 +8101,34 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O103" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8136,32 +8138,32 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -8171,35 +8173,35 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P104" s="15" t="n">
         <v>0</v>
@@ -8208,12 +8210,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8223,13 +8225,11 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v/>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
@@ -8248,23 +8248,23 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
@@ -8475,18 +8475,18 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8496,12 +8496,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Adaptation Modèle et FDS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8511,11 +8511,13 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8529,28 +8531,28 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
+        <v>1.55</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8566,12 +8568,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8581,38 +8583,54 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F110" s="14" t="inlineStr"/>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H110" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H110" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr"/>
-      <c r="M110" s="14" t="inlineStr"/>
+        <v>1.55</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="M110" s="14" t="inlineStr">
+        <is>
+          <t>00144857</t>
+        </is>
+      </c>
       <c r="N110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8622,12 +8640,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Adaptation Modèle et FDS</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8637,7 +8655,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8660,23 +8678,23 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8692,12 +8710,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8707,52 +8725,38 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F112" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="inlineStr"/>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H112" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H112" s="14" t="inlineStr"/>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27017</t>
-        </is>
-      </c>
-      <c r="M112" s="14" t="inlineStr">
-        <is>
-          <t>00141205</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
       <c r="N112" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8762,22 +8766,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8800,23 +8804,23 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8832,22 +8836,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24880</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[CD 76] - Modélisation complémentaire 28H</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>DEPARTEMENT DE LA SEINE MARITIME (CD 76)</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8865,49 +8869,49 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27048</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>0014120</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>416.188</v>
+        <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8917,13 +8921,11 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v/>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
@@ -8932,39 +8934,39 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O115" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8974,22 +8976,22 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -9007,28 +9009,28 @@
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9044,22 +9046,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9082,23 +9084,23 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
@@ -9114,22 +9116,22 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9152,23 +9154,23 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
@@ -9184,12 +9186,12 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9199,7 +9201,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9222,44 +9224,44 @@
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="12" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P119" s="12" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9269,11 +9271,13 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
-        </is>
-      </c>
-      <c r="E120" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
@@ -9282,33 +9286,33 @@
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
@@ -9324,12 +9328,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22494</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9339,7 +9343,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9352,27 +9356,35 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L121" s="11" t="inlineStr"/>
-      <c r="M121" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27570</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>493613</t>
+        </is>
+      </c>
       <c r="N121" s="12" t="n">
         <v>0</v>
       </c>
@@ -9386,12 +9398,12 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
@@ -9401,7 +9413,7 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9419,28 +9431,28 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9456,22 +9468,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9489,34 +9501,34 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O123" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9526,22 +9538,22 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21548</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[Evreux] AME</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9559,28 +9571,28 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28039</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>477841</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
@@ -9596,22 +9608,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9634,23 +9646,23 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>8.25</v>
+        <v>0.06</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
@@ -9666,12 +9678,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22494</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9681,7 +9693,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9694,7 +9706,7 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr">
@@ -9704,25 +9716,17 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M126" s="14" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
       <c r="N126" s="15" t="n">
         <v>0</v>
       </c>
@@ -9736,22 +9740,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9774,29 +9778,29 @@
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O127" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9806,12 +9810,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9821,7 +9825,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9839,34 +9843,34 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="15" t="n">
@@ -9876,12 +9880,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-21548</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Evreux] AME</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9891,7 +9895,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9914,23 +9918,23 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28039</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>477841</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
@@ -9946,22 +9950,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9984,23 +9988,23 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>1</v>
+        <v>8.25</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10016,12 +10020,12 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -10031,7 +10035,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10049,28 +10053,28 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K131" s="11" t="n">
         <v>1</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10086,22 +10090,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10114,7 +10118,7 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
@@ -10124,21 +10128,29 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr"/>
-      <c r="M132" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M132" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O132" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="15" t="n">
@@ -10148,12 +10160,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10163,7 +10175,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10176,7 +10188,7 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -10186,17 +10198,25 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr"/>
-      <c r="M133" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N133" s="12" t="n">
         <v>0</v>
       </c>
@@ -10210,22 +10230,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10233,7 +10253,7 @@
       </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
@@ -10243,34 +10263,34 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="15" t="n">
@@ -10280,22 +10300,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10313,28 +10333,28 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
@@ -10350,22 +10370,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10383,28 +10403,28 @@
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
@@ -10420,22 +10440,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10448,7 +10468,7 @@
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -10458,29 +10478,21 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M137" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O137" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="12" t="n">
@@ -10490,22 +10502,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-17710</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Saint Lo] Migration</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>Saint Lo</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10513,25 +10525,29 @@
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G138" s="14" t="inlineStr"/>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>25/11/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.75</v>
+        <v>13.08</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10548,22 +10564,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-16116</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10571,36 +10587,44 @@
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L139" s="11" t="inlineStr"/>
-      <c r="M139" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N139" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O139" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="12" t="n">
@@ -10610,22 +10634,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10638,7 +10662,7 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
@@ -10648,17 +10672,25 @@
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr"/>
-      <c r="M140" s="14" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M140" s="14" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10672,12 +10704,12 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -10687,7 +10719,7 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10700,7 +10732,7 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -10710,17 +10742,25 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr"/>
-      <c r="M141" s="11" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10734,22 +10774,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10762,31 +10802,39 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr"/>
-      <c r="M142" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M142" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N142" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O142" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="15" t="n">
@@ -10796,22 +10844,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-17710</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Saint Lo] Migration</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Saint Lo</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10819,40 +10867,28 @@
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G143" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr"/>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>25/11/2024</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
@@ -10866,22 +10902,22 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10897,17 +10933,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H144" s="14" t="inlineStr"/>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L144" s="14" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -10924,12 +10964,12 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
@@ -10939,7 +10979,7 @@
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -10957,30 +10997,22 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="12" t="n">
         <v>0</v>
       </c>
@@ -10994,12 +11026,12 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
@@ -11009,13 +11041,11 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E146" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t xml:space="preserve">Asnieres sur Seine </t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="n">
+        <v/>
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
@@ -11034,14 +11064,14 @@
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L146" s="14" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -11058,24 +11088,26 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C147" s="11" t="inlineStr"/>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v/>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
@@ -11094,14 +11126,14 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="L147" s="11" t="inlineStr"/>
       <c r="M147" s="11" t="inlineStr"/>
@@ -11118,21 +11150,27 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="C148" s="14" t="inlineStr"/>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E148" s="14" t="inlineStr"/>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="n">
+        <v/>
+      </c>
       <c r="F148" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11143,24 +11181,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H148" s="14" t="inlineStr"/>
+      <c r="H148" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="L148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M148" s="14" t="inlineStr"/>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M148" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
@@ -11174,21 +11220,27 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="C149" s="11" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="E149" s="11" t="inlineStr"/>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v/>
+      </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11196,20 +11248,20 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -11226,21 +11278,27 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
-        </is>
-      </c>
-      <c r="C150" s="14" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
-        </is>
-      </c>
-      <c r="E150" s="14" t="inlineStr"/>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="n">
+        <v/>
+      </c>
       <c r="F150" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11248,29 +11306,33 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H150" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H150" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K150" s="14" t="n">
         <v>0.25</v>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34778</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M150" s="14" t="inlineStr">
         <is>
-          <t>00172868</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N150" s="15" t="n">
@@ -11286,21 +11348,29 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C151" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E151" s="11" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11308,31 +11378,27 @@
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H151" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L151" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M151" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr"/>
       <c r="N151" s="12" t="n">
         <v>0</v>
       </c>
@@ -11346,21 +11412,25 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr"/>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
-        </is>
-      </c>
-      <c r="E152" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11368,20 +11438,24 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H152" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H152" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L152" s="14" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -11396,31 +11470,311 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="17" t="inlineStr">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1339</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr"/>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr"/>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr"/>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J153" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K153" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr"/>
+      <c r="N153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1334</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MOUY</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr"/>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MOUY</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr"/>
+      <c r="F154" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G154" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr"/>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K154" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L154" s="14" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+      <c r="N154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1315</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr"/>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr"/>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr"/>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="J155" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K155" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M155" s="11" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
+      <c r="N155" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr"/>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr"/>
+      <c r="F156" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G156" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H156" s="14" t="inlineStr"/>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K156" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L156" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N156" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr"/>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr"/>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr"/>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="J157" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K157" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L157" s="11" t="inlineStr"/>
+      <c r="M157" s="11" t="inlineStr"/>
+      <c r="N157" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B153" s="17" t="inlineStr"/>
-      <c r="C153" s="17" t="inlineStr"/>
-      <c r="D153" s="17" t="inlineStr"/>
-      <c r="E153" s="17" t="inlineStr"/>
-      <c r="F153" s="17" t="inlineStr"/>
-      <c r="G153" s="17" t="inlineStr"/>
-      <c r="H153" s="17" t="inlineStr"/>
-      <c r="I153" s="17" t="inlineStr"/>
-      <c r="J153" s="17" t="inlineStr"/>
-      <c r="K153" s="17" t="inlineStr"/>
-      <c r="L153" s="17" t="inlineStr"/>
-      <c r="M153" s="17" t="inlineStr"/>
-      <c r="N153" s="18" t="n">
+      <c r="B158" s="17" t="inlineStr"/>
+      <c r="C158" s="17" t="inlineStr"/>
+      <c r="D158" s="17" t="inlineStr"/>
+      <c r="E158" s="17" t="inlineStr"/>
+      <c r="F158" s="17" t="inlineStr"/>
+      <c r="G158" s="17" t="inlineStr"/>
+      <c r="H158" s="17" t="inlineStr"/>
+      <c r="I158" s="17" t="inlineStr"/>
+      <c r="J158" s="17" t="inlineStr"/>
+      <c r="K158" s="17" t="inlineStr"/>
+      <c r="L158" s="17" t="inlineStr"/>
+      <c r="M158" s="17" t="inlineStr"/>
+      <c r="N158" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O153" s="18" t="n">
+      <c r="O158" s="18" t="n">
         <v>25176.268</v>
       </c>
-      <c r="P153" s="18" t="n">
-        <v>148.91</v>
+      <c r="P158" s="18" t="n">
+        <v>145.9</v>
       </c>
     </row>
   </sheetData>
@@ -11574,6 +11928,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12655,7 +13014,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>85.92</v>
+        <v>89.42</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>28.92</v>
@@ -12664,7 +13023,7 @@
         <v>11.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>126.08</v>
+        <v>129.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>20.42</v>
@@ -12674,7 +13033,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
     </row>
@@ -12716,7 +13075,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>70.75</v>
+        <v>71.75</v>
       </c>
     </row>
   </sheetData>
@@ -12880,7 +13239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12904,7 +13263,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 21 commande(s)</t>
+          <t>Épics créées ce mois — 22 commande(s)</t>
         </is>
       </c>
     </row>
@@ -12959,22 +13318,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35758</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35752</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -12984,7 +13343,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -12994,32 +13353,32 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00181622</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35758</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35752</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -13029,7 +13388,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -13039,32 +13398,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00181622</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>6285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35747</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35743</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>COMMUNE D'EYSINES</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -13074,34 +13433,42 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>00181626</t>
+        </is>
+      </c>
       <c r="I7" s="25" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35733</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35727</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNE DE VIEUX BOUCAU</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -13111,7 +13478,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -13121,7 +13488,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00181531</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
@@ -13131,22 +13498,22 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35703</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35696</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE HARFLEUR</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -13166,32 +13533,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00181438</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -13211,7 +13578,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
@@ -13221,22 +13588,22 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35606</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -13256,32 +13623,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00181049</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35703</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35696</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARFLEUR</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -13301,7 +13668,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00181438</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -13311,22 +13678,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35733</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35727</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIEUX BOUCAU</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -13346,32 +13713,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00181531</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35747</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35743</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -13381,7 +13748,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -13391,7 +13758,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00181626</t>
+          <t>00181049</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
@@ -13401,22 +13768,22 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35672</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35666</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -13426,7 +13793,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -13436,7 +13803,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00181382</t>
+          <t>00180931</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
@@ -13446,22 +13813,22 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -13474,39 +13841,31 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>00179700</t>
-        </is>
-      </c>
+      <c r="G16" s="11" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr"/>
       <c r="I16" s="26" t="n">
-        <v>28915.01</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -13526,32 +13885,32 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>6382.5</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35687</t>
+          <t>PDMDEP-35464</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35683</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -13571,32 +13930,32 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00181396</t>
+          <t>00180631</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>2333.33</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -13606,7 +13965,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -13616,7 +13975,7 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
@@ -13626,22 +13985,22 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35719</t>
+          <t>PDMDEP-35771</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35715</t>
+          <t>PDMDEP-35767</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Commune de Dunkerque</t>
+          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -13661,7 +14020,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>00181457</t>
+          <t>00181751</t>
         </is>
       </c>
       <c r="I20" s="26" t="n">
@@ -13716,22 +14075,22 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -13751,32 +14110,32 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="I22" s="26" t="n">
-        <v>895</v>
+        <v>6382.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -13786,7 +14145,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -13796,32 +14155,32 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="I23" s="25" t="n">
-        <v>0</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35719</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35715</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>Commune de Dunkerque</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -13841,32 +14200,32 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00181457</t>
         </is>
       </c>
       <c r="I24" s="26" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -13886,38 +14245,62 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>00180506</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I25" s="25" t="n">
-        <v>3974</v>
+        <v>895</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>21 commande(s)</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>52730</v>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35622</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35618</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Commune de la Roche-sur-Yon</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>00181123</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" s="17" t="n"/>
@@ -13928,17 +14311,17 @@
       <c r="G27" s="17" t="n"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>9 commande(s)</t>
+          <t>22 commande(s)</t>
         </is>
       </c>
       <c r="I27" s="24" t="n">
-        <v>14880</v>
+        <v>52730</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B28" s="17" t="n"/>
@@ -13949,10 +14332,31 @@
       <c r="G28" s="17" t="n"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
+          <t>10 commande(s)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>14880</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
           <t>12 commande(s)</t>
         </is>
       </c>
-      <c r="I28" s="24" t="n">
+      <c r="I29" s="24" t="n">
         <v>37850</v>
       </c>
     </row>
@@ -13967,7 +14371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -13988,7 +14392,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6 clôture(s) : 6 projet(s), 0 rework</t>
+          <t>7 clôture(s) : 7 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -14178,59 +14582,89 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-32442</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-33699</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assist</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="n">
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n">
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n">
         <v>0</v>
       </c>
     </row>
